--- a/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/CCD_BEFTA_JURISDICTION1.xlsx
+++ b/src/main/resources/uk/gov/hmcts/ccd/test_definitions/excel/CCD_BEFTA_JURISDICTION1.xlsx
@@ -806,10 +806,10 @@
     <t>BEFTA_SOLICITOR_1</t>
   </si>
   <si>
-    <t>OGD_DWP_PROFILE</t>
-  </si>
-  <si>
-    <t>SOLICITOR_PROFILE</t>
+    <t>BEFTA_OGD_DWP_PROFILE</t>
+  </si>
+  <si>
+    <t>BEFTA_SOLICITOR_PROFILE</t>
   </si>
   <si>
     <t>AccessTypeRole</t>
